--- a/quizzes/020_quantum_numbers_knowledge_quiz--quizzes.xlsx
+++ b/quizzes/020_quantum_numbers_knowledge_quiz--quizzes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>quantum_numbers_knowledge_quiz_start</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quiz_question_2</t>
+          <t>quantum_numbers_definition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>What is Quantum Numbers?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>quantum_numbers_significance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>What is the significance of Quantum Numbers?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quiz_question_3</t>
+          <t>quantum_numbers_relationship_wave_functions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>How are Quantum Numbers related to Wave Functions?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>answer_3</t>
+          <t>quantum_numbers_difference_wave_functions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>What is the difference between Quantum Numbers and Wave Functions?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>quiz_question_4</t>
+          <t>quantum_numbers_number_of_atoms</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>How many Quantum Numbers can an atom have?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>answer_4</t>
+          <t>quantum_numbers_properties</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>What are the properties of Quantum Numbers?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quiz_question_5</t>
+          <t>quantum_numbers_applications_chemistry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>What is the role of Quantum Numbers in Quantum Chemistry?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>answer_5</t>
+          <t>quantum_numbers_effects_electron_behavior</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>How do Quantum Numbers affect the behavior of electrons?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>quiz_question_6</t>
+          <t>example_quantum_number</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>Provide an example of an atomic orbital with a specific Quantum Number?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>answer_6</t>
+          <t>quantum_numbers_wave_functions_relationship</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>How are Quantum Numbers related to Wave Functions in Quantum Mechanics?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>quiz_question_7</t>
+          <t>quantum_numbers_wave_functions_significance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>What is the significance of Wave Functions in Quantum Numbers?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>answer_7</t>
+          <t>quantum_numbers_wave_functions_calculations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Can Wave Functions be used to calculate Quantum Numbers?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>quiz_question_8</t>
+          <t>atomic_orbitals_quantum_numbers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>What is the relationship between Quantum Numbers and Atomic Orbitals?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>answer_8</t>
+          <t>quantum_numbers_energy_levels</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>How do Quantum Numbers affect the energy levels of an atom?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>quiz_question_9</t>
+          <t>quantum_numbers_electron_spin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>How do Quantum Numbers affect the spin of an electron?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>answer_9</t>
+          <t>quantum_numbers_magnetic_moment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Can Quantum Numbers influence the magnetic moment of an electron?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>quiz_question_10</t>
+          <t>quantum_numbers_computing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>Can Quantum Numbers be used in Quantum Computing?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>answer_10</t>
+          <t>quantum_numbers_information_processing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>How do Quantum Numbers relate to Quantum Information Theory?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>quiz_question_11</t>
+          <t>quantum_numbers_error_correction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>Can Quantum Numbers be used in Quantum Error Correction?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>answer_11</t>
+          <t>quantum_numbers_entanglement</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Can Quantum Numbers be used to describe Quantum Entanglement?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>quiz_question_12</t>
+          <t>quantum_numbers_supremacy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>Can Quantum Numbers be used to predict Quantum Supremacy?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>answer_12</t>
+          <t>quantum_numbers_information_preservation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Can Quantum Numbers be used to preserve Quantum Information?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>quiz_question_13</t>
+          <t>quantum_numbers_error_mitigation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Quantum Numbers</t>
+          <t>Can Quantum Numbers be used to mitigate Quantum Errors?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>answer_13</t>
+          <t>quantum_numbers_error_detection</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Can Quantum Numbers be used to detect Quantum Errors?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
